--- a/CUADRO DE PRUEBAS.xlsx
+++ b/CUADRO DE PRUEBAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C265AFA3-8303-42AF-86A3-85E7F6F6699E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5C65B-D0A7-4438-8C94-50EB2D8767BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="59">
   <si>
     <t>XBEE</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>ENERGY + ADAPTIVE</t>
+  </si>
+  <si>
+    <t>71.7 ms</t>
+  </si>
+  <si>
+    <t>61.9 mAh</t>
   </si>
 </sst>
 </file>
@@ -834,10 +840,18 @@
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="2">

--- a/CUADRO DE PRUEBAS.xlsx
+++ b/CUADRO DE PRUEBAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA01E13-CFE8-430E-8B9E-E9BAB2B09055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8948CE7-15D7-4B87-AEAD-0B05014C3765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="114">
   <si>
     <t>XBEE</t>
   </si>
@@ -99,9 +98,6 @@
     <t>CONSUMO</t>
   </si>
   <si>
-    <t>TIEMPO EN EL ESTADO</t>
-  </si>
-  <si>
     <t>ADAPTIVE</t>
   </si>
   <si>
@@ -291,9 +287,6 @@
     <t>43.1 mAh</t>
   </si>
   <si>
-    <t>54.6 mAh</t>
-  </si>
-  <si>
     <t>38.6 mAh</t>
   </si>
   <si>
@@ -307,6 +300,87 @@
   </si>
   <si>
     <t>42.8 mAh</t>
+  </si>
+  <si>
+    <t>54.6 ms</t>
+  </si>
+  <si>
+    <t>90 ms</t>
+  </si>
+  <si>
+    <t>34.3 mAh</t>
+  </si>
+  <si>
+    <t>33.2 ms</t>
+  </si>
+  <si>
+    <t>45.6 mAh</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>18.7 ms</t>
+  </si>
+  <si>
+    <t>68.2 mAh</t>
+  </si>
+  <si>
+    <t>21.6 ms</t>
+  </si>
+  <si>
+    <t>73.4 mAh</t>
+  </si>
+  <si>
+    <t>74.7 mAh</t>
+  </si>
+  <si>
+    <t>31.7 ms</t>
+  </si>
+  <si>
+    <t>79.6 mAh</t>
+  </si>
+  <si>
+    <t>67.4 mAh</t>
+  </si>
+  <si>
+    <t>84 ms</t>
+  </si>
+  <si>
+    <t>74.5 mAh</t>
+  </si>
+  <si>
+    <t>66.3 mAh</t>
+  </si>
+  <si>
+    <t>74.2 mAh</t>
+  </si>
+  <si>
+    <t>45.4 mAh</t>
+  </si>
+  <si>
+    <t>20.3 ms</t>
+  </si>
+  <si>
+    <t>20.4 mAh</t>
+  </si>
+  <si>
+    <t>21 mAh</t>
+  </si>
+  <si>
+    <t>31.1 mAh</t>
+  </si>
+  <si>
+    <t>25.2 ms</t>
+  </si>
+  <si>
+    <t>20.3 mAh</t>
+  </si>
+  <si>
+    <t>89 ms</t>
+  </si>
+  <si>
+    <t>34.6 mAh</t>
   </si>
 </sst>
 </file>
@@ -393,17 +467,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FA4C8B-A099-47B7-BA2E-F5A7D41331DF}">
-  <dimension ref="B1:I40"/>
+  <dimension ref="B1:I38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -751,14 +826,14 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="6"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="7"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
@@ -806,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>14</v>
@@ -832,7 +907,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>14</v>
@@ -843,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -852,16 +927,16 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -869,7 +944,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -878,16 +953,16 @@
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -895,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
@@ -904,16 +979,16 @@
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -921,7 +996,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
@@ -930,16 +1005,16 @@
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -947,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -956,16 +1031,16 @@
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -973,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -982,16 +1057,16 @@
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -999,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -1008,16 +1083,16 @@
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -1025,7 +1100,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1109,16 @@
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
@@ -1051,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -1060,16 +1135,16 @@
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
@@ -1077,7 +1152,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -1086,23 +1161,23 @@
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>13</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -1115,20 +1190,20 @@
         <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>14</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -1138,24 +1213,24 @@
         <v>17</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>15</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>20</v>
+      <c r="C17" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
@@ -1164,24 +1239,24 @@
         <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>16</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>20</v>
+      <c r="C18" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>9</v>
@@ -1190,50 +1265,50 @@
         <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>17</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>35</v>
+      <c r="C19" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>18</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>57</v>
+      <c r="C20" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>9</v>
@@ -1242,24 +1317,24 @@
         <v>17</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>19</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>28</v>
+      <c r="C21" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>6</v>
@@ -1268,24 +1343,24 @@
         <v>17</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>20</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>28</v>
+      <c r="C22" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>9</v>
@@ -1294,24 +1369,24 @@
         <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>21</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>27</v>
+      <c r="C23" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>6</v>
@@ -1320,24 +1395,24 @@
         <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>22</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>27</v>
+      <c r="C24" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>9</v>
@@ -1346,50 +1421,50 @@
         <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>23</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>29</v>
+      <c r="C25" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>84</v>
       </c>
+      <c r="G25" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>85</v>
+        <v>23</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="5">
         <v>24</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>30</v>
+      <c r="C26" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>9</v>
@@ -1398,21 +1473,21 @@
         <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>5</v>
@@ -1423,16 +1498,22 @@
       <c r="E27" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="H27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>5</v>
@@ -1443,19 +1524,25 @@
       <c r="E28" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="H28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>6</v>
@@ -1463,19 +1550,25 @@
       <c r="E29" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="H29" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>9</v>
@@ -1483,22 +1576,28 @@
       <c r="E30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="H30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>0</v>
@@ -1506,16 +1605,16 @@
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>9</v>
@@ -1526,16 +1625,16 @@
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>6</v>
@@ -1543,19 +1642,25 @@
       <c r="E33" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="H33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>9</v>
@@ -1563,19 +1668,25 @@
       <c r="E34" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="H34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>6</v>
@@ -1583,19 +1694,25 @@
       <c r="E35" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="H35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>9</v>
@@ -1603,22 +1720,28 @@
       <c r="E36" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="H36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>0</v>
@@ -1626,16 +1749,16 @@
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>9</v>
@@ -1646,49 +1769,9 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="4">
-        <v>41</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="4"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="4">
-        <v>42</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/CUADRO DE PRUEBAS.xlsx
+++ b/CUADRO DE PRUEBAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8948CE7-15D7-4B87-AEAD-0B05014C3765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD5AD92-2BD1-4B6F-9F34-1F64982D2207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="126">
   <si>
     <t>XBEE</t>
   </si>
@@ -381,6 +381,42 @@
   </si>
   <si>
     <t>34.6 mAh</t>
+  </si>
+  <si>
+    <t>34.3 ms</t>
+  </si>
+  <si>
+    <t>29.5 mAh</t>
+  </si>
+  <si>
+    <t>16 mAh</t>
+  </si>
+  <si>
+    <t>30 mAh</t>
+  </si>
+  <si>
+    <t>15 ms</t>
+  </si>
+  <si>
+    <t>19.8 mAh</t>
+  </si>
+  <si>
+    <t>19.27 mAh</t>
+  </si>
+  <si>
+    <t>30.2 mAh</t>
+  </si>
+  <si>
+    <t>18.4 ms</t>
+  </si>
+  <si>
+    <t>36 ms</t>
+  </si>
+  <si>
+    <t>13.2 mAh</t>
+  </si>
+  <si>
+    <t>24.0 mAh</t>
   </si>
 </sst>
 </file>
@@ -475,10 +511,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -826,14 +862,14 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7" t="s">
+      <c r="G1" s="8"/>
+      <c r="H1" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="7"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
@@ -1585,7 +1621,7 @@
       <c r="H30" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1602,12 +1638,18 @@
       <c r="E31" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="H31" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I31" s="4"/>
+      <c r="I31" s="4" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1622,12 +1664,18 @@
       <c r="E32" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="H32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I32" s="4"/>
+      <c r="I32" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
@@ -1746,12 +1794,18 @@
       <c r="E37" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="H37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="4"/>
+      <c r="I37" s="4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
@@ -1766,12 +1820,18 @@
       <c r="E38" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
+      <c r="F38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="H38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I38" s="4"/>
+      <c r="I38" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/CUADRO DE PRUEBAS.xlsx
+++ b/CUADRO DE PRUEBAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\OneDrive\Documentos\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52C9AA4-F8B7-4776-A1AD-637CE0A26C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ED6034-9C22-4707-B912-1E4626D2EF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
+    <workbookView xWindow="8256" yWindow="3360" windowWidth="14784" windowHeight="8880" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,22 +658,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FA4C8B-A099-47B7-BA2E-F5A7D41331DF}">
   <dimension ref="B1:N38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="11.5546875" style="4"/>
-    <col min="3" max="3" width="28.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.5546875" style="4"/>
-    <col min="8" max="8" width="11.44140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="4"/>
-    <col min="10" max="10" width="29.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.5546875" style="4"/>
+    <col min="1" max="2" width="11.59765625" style="4"/>
+    <col min="3" max="3" width="28.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.59765625" style="4"/>
+    <col min="8" max="8" width="11.3984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" style="4"/>
+    <col min="10" max="10" width="29.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.59765625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -693,7 +693,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -734,7 +734,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14">
       <c r="B3" s="6">
         <v>1</v>
       </c>
@@ -780,7 +780,7 @@
         <v>2.4801125442188385</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14">
       <c r="B4" s="6">
         <v>2</v>
       </c>
@@ -826,7 +826,7 @@
         <v>5.3691885156862478</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14">
       <c r="B5" s="6">
         <v>3</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9.3411125710612293</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14">
       <c r="B6" s="6">
         <v>4</v>
       </c>
@@ -918,7 +918,7 @@
         <v>2.7520524640072783</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14">
       <c r="B7" s="6">
         <v>5</v>
       </c>
@@ -964,7 +964,7 @@
         <v>38.549808141944197</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14">
       <c r="B8" s="6">
         <v>6</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>38.548117713481581</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14">
       <c r="B9" s="6">
         <v>7</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>2.4772034552808218</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14">
       <c r="B10" s="6">
         <v>8</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>5.9352268046856258</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14">
       <c r="B11" s="6">
         <v>9</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>5.3418733719273304</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14">
       <c r="B12" s="6">
         <v>10</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>2.327757328949533</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14">
       <c r="B13" s="6">
         <v>11</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>33.590590499987009</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14">
       <c r="B14" s="6">
         <v>12</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>37.861770446960882</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14">
       <c r="B15" s="7">
         <v>13</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>1.7565884052287533</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14">
       <c r="B16" s="7">
         <v>14</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>2.3148094654965465</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14">
       <c r="B17" s="7">
         <v>15</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>2.4029206699073584</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14">
       <c r="B18" s="7">
         <v>16</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>5.4537399386552581</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14">
       <c r="B19" s="7">
         <v>17</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>20.031544316098557</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14">
       <c r="B20" s="7">
         <v>18</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>19.83753355828345</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14">
       <c r="B21" s="7">
         <v>19</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>2.3864059836632676</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14">
       <c r="B22" s="7">
         <v>20</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>5.1062075783162717</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14">
       <c r="B23" s="7">
         <v>21</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>2.3864068882997542</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14">
       <c r="B24" s="7">
         <v>22</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>2.5070195792790217</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14">
       <c r="B25" s="7">
         <v>23</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>14.171201564279349</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14">
       <c r="B26" s="7">
         <v>24</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>19.838272918746725</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14">
       <c r="B27" s="10">
         <v>25</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>3.0909664535102075</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14">
       <c r="B28" s="10">
         <v>26</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>10.262010992338087</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14">
       <c r="B29" s="10">
         <v>27</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>2.7889270684399272</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14">
       <c r="B30" s="10">
         <v>28</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>6.0737843033085257</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14">
       <c r="B31" s="10">
         <v>29</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>13.102411323842459</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14">
       <c r="B32" s="10">
         <v>30</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>15.782311791465672</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:14">
       <c r="B33" s="10">
         <v>31</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>3.0547353682039398</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:14">
       <c r="B34" s="10">
         <v>32</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>9.9205013282909515</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:14">
       <c r="B35" s="10">
         <v>33</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>3.1422747746169359</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14">
       <c r="B36" s="10">
         <v>34</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>10.212136027116632</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:14">
       <c r="B37" s="10">
         <v>35</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>10.521793413444652</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:14">
       <c r="B38" s="10">
         <v>36</v>
       </c>
